--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。rtf_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。rtf_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>tfl_plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>tfl_plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col の値ごとに改ページ（tfl_plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>plan_blanks() の where / first / last / counted。</t>
+          <t>tfl_plan_blanks() の where / first / last / counted。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>tfl_plan_stub() の vars / into / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
+          <t>tfl_plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>以下は表の周りの定義。read_report_spec(c(report.xlsx; tables.xlsx); output_id = ) で 1 冊でも分冊でも読める。同じシートに行があるのは 1 冊だけにする（空のシートと study は重なってよい）。rtf_report(spec; plan) で rtf_document、report_path(spec) で出力先。</t>
+          <t>以下は表の周りの定義。tfl_read_report_spec(c(report.xlsx; tables.xlsx); output_id = ) で 1 冊でも分冊でも読める。同じシートに行があるのは 1 冊だけにする（空のシートと study は重なってよい）。tfl_report(spec; plan) で rtf_document、tfl_report_path(spec) で出力先。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_table_plan(data; tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_table_plan(data; tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tfl_plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tfl_plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（tfl_plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tfl_plan_blanks() の where / first / last / counted。</t>
+          <t>plan_blanks() の where / first / last / counted。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tfl_plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tfl_plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
+          <t>plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cells（テンプレートでセルを作る）/ rows（統計量ごとに 1 行、生の値）。</t>
+          <t>cells（テンプレートでセルを作る）/ rows（統計量ごとに 1 行、生の値）。plan_cells(stats = )。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>stats = rows のときの値。stat（数値）/ stat_fmt（cards 整形済み文字列）。</t>
+          <t>stats = rows のときの値。stat（数値）/ stat_fmt（cards 整形済み文字列）。plan_cells(value = )。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cols が複数のとき列名をつなぐ文字。既定は ____。</t>
+          <t>cols が複数のとき値の列名をつなぐ文字。既定は ____。columns シートはこの名前で列を指す。plan_columns(sep = )。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>列方向に合計して .sort_stat 列にする統計量名。</t>
+          <t>列方向に合計して並べ替えに使う統計量名。plan_sort(stat = )。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ページ（検査項目など）で分けた表のヘッダー {n} がどの母集団か。page = そのページの母集団（その検査を受けた人）/ table = 解析対象集団（ページキーを持たない ARD 行）。両方なら n = page | N = table で {n} と {N}。空欄 = page（両方あって食い違えば警告）。どちらも ARD に入れておくこと。</t>
+          <t>ページ（検査項目など）で分けた表のヘッダー {n} がどの母集団か。page = そのページの母集団（その検査を受けた人）/ table = 解析対象集団（ページキーを持たない ARD 行）。両方なら n = page | N = table で {n} と {N}。空欄 = page（両方あって食い違えば警告）。どちらも ARD に入れておくこと。plan_col_header(values = list(n = ...))。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>stats = rows の帳票だけ：統計量ごとの表示桁。row = 統計量名（ラベル列の値）、digits / signif を書く（fmt_numeric と同じ）。variable / context は空欄。</t>
+          <t>stats = rows の帳票だけ：統計量ごとの表示桁。row = 統計量名（ラベル列の値）、digits / signif を書く（plan_digits(.rows = ) になる。signif は 4s のように有効桁）。variable / context は空欄。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pages_max_rows / pages_split / pages_by / pages_min_group_rows / pages_cont_label</t>
+          <t>pages_max_rows / pages_split / pages_min_group_rows / pages_cont_label</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>group_col / group_mode / group_collapse</t>
+          <t>group_mode / group_collapse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>plan_row_group() の mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。グループの列は行キーから決まる。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>group_page / group_show</t>
+          <t>group_page / group_col / group_keep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col（空欄なら一番外の行キー）の値ごとに改ページ（plan_paginate_group の col / keep）。group_keep = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRUE / FALSE</t>
+          <t>TRUE / PARAM / FALSE</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>stub_vars / stub_into / stub_indent / stub_summary / stub_before</t>
+          <t>stub_vars / stub_name / stub_indent / stub_summary / stub_before</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>plan_stub() の vars / name / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 行 = 印字される列 1 つ。列は名前で指定（畳んだスタブは stub_into の名前）。.values = 展開された値の列すべて。</t>
+          <t>1 行 = 印字される列 1 つ。列は名前で指定（畳んだスタブは stub_name の名前、値の列は tables の sep でつないだ名前）。.values = 展開された値の列すべて。</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TRUE で行見出しの列。</t>
+          <t>TRUE で行見出しの列。plan_columns(row_title = )。</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 行 = 1 帳票。border / align_count_pct / auto_width / row_height_twips / header_row_height_twips / blank_row_height_twips / font / font_size_half_points / table_align / cell_valign（rtftable と同じ引数）。</t>
+          <t>1 行 = 1 帳票。border / align_count_pct / row_height_twips / header_row_height_twips / blank_row_height_twips / font / font_size_half_points / table_align / cell_valign（plan_style と同じ引数）。auto_width は plan_columns(auto_width = ) になる。</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2821,7 +2821,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2842,105 +2842,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pages_by</t>
+          <t>pages_min_group_rows</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pages_min_group_rows</t>
+          <t>pages_cont_label</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>pages_cont_label</t>
+          <t>group_col</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>group_col</t>
+          <t>group_mode</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>group_mode</t>
+          <t>group_collapse</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>group_collapse</t>
+          <t>group_page</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>group_page</t>
+          <t>group_keep</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>group_show</t>
+          <t>blank_where</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>blank_where</t>
+          <t>blank_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>blank_first</t>
+          <t>blank_last</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>blank_last</t>
+          <t>blank_counted</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>blank_counted</t>
+          <t>stub_vars</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>stub_vars</t>
+          <t>stub_name</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>stub_into</t>
+          <t>stub_indent</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>stub_indent</t>
+          <t>stub_summary</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>stub_summary</t>
+          <t>stub_before</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>stub_before</t>
+          <t>colpages_every</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>colpages_every</t>
+          <t>colpages_at</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>colpages_at</t>
+          <t>colpages_keep</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>colpages_carry</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>colpages_order</t>
         </is>
@@ -2995,7 +2990,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3026,32 +3021,82 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>row_height_exact</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>header_row_height_twips</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>blank_row_height_twips</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cell_padding_left_twips</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cell_padding_right_twips</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>font</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>font_size_half_points</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>table_align</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cell_valign</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>markup</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>blank_row_normalize</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>border_header</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>border_spanning</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>border_body</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>border_first_row</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>border_last_row</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -32,7 +32,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">id: the subject key (USUBJID); output: where the study ARD goes</t>
+          <t xml:space="preserve">The fact: rounding (r: round half to even; sas: round half away from zero; blank: options(rtfreporter.rounding)); output_path (the folder of the RTF files); program_dir (the folder of the programs, for {PROGRAM}); ARD: id (the subject key; default USUBJID), output (the study ARD's file; default output/ard/ard.rds), source (R files of the study's own analysis functions, relative to the study folder, | between them).
+Example: rounding</t>
         </r>
       </text>
     </comment>
@@ -44,7 +45,725 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">id: the subject key (USUBJID); output: where the study ARD goes</t>
+          <t xml:space="preserve">Its value, as text.
+Example: sas</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">table / listing / figure; blank: table.
+Example: listing</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The RTF file, relative to the study key output_path; {output_id} is the report's id; blank: {output_id}.rtf.
+Example: {output_id}.rtf</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The program's name, joined to program_dir for {PROGRAM}; blank: {output_id}.
+Example: {output_id}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: each named table a section with its name in the page header (rtf_tables(auto_section = )); blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">left / center / right: the section label (rtf_tables(section_label_align = )); blank: left.
+Example: left</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: each named table's name as its last title line (rtf_tables(auto_title = )); blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">left / center / right: that title line (rtf_tables(title_label_align = )); blank: left.
+Example: center</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The table's font size in half-points (18 = 9 pt) (rtf_tables(font_size_half_points = )); blank: the document's.
+Example: 14</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The titles' font size in half-points; blank: the document's.
+Example: 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The footnotes' font size in half-points; blank: the document's.
+Example: 14</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: FALSE drops the running page header for this report, the study's default lines included; blank: TRUE.
+Example: FALSE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: FALSE drops the running page footer, likewise; blank: TRUE.
+Example: FALSE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A column for people, on any sheet; never read. Any other column a sheet does not read is an error (a mistyped header).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">letter / legal / A4 / A3 / A5; blank: letter.
+Example: A4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">landscape / portrait; blank: landscape.
+Example: portrait</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Page width in inches (wins over paper_size); blank: the paper's.
+Example: 11</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Page height in inches; blank: the paper's.
+Example: 8.5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Top margin in inches; blank: 0.75.
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Bottom margin in inches; blank: 0.75.
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Left margin in inches; blank: 0.75.
+Example: 0.5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Right margin in inches; blank: 0.75.
+Example: 0.5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">From the page's top edge to the running header, in inches; blank: the top margin.
+Example: 0.5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">From the page's bottom edge to the running footer, in inches; blank: the bottom margin.
+Example: 0.5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The body font size in half-points (18 = 9 pt); blank: rtfreporter's option.
+Example: 18</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">text (centred paragraphs) / table (a content-width one-column table); blank: text.
+Example: table</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">table (content-width, with the separator rule) / text (paragraphs); blank: table.
+Example: text</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The title block's width: content / page / a fraction of the writable width / twips; blank: content.
+Example: page</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The footnote block's width, as title_width; blank: content.
+Example: page</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Cell-text markup for the whole document: script / relational / all / none; blank: script.
+Example: all</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The line number, a whole number (1 = the top).
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the left; tokens work.
+Example: Protocol XYZ-001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text in the centre.
+Example: CONFIDENTIAL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the right.
+Example: Page {PAGE} of {TOTAL_PAGES}</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The line number.
+Example: 99</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the left.
+Example: {PROGRAM}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text in the centre.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the right.
+Example: Generated on: {DATETIME}</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The line number.
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the left.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text in the centre.
+Example: Table 14.1.1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the right.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The line number.
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the left.
+Example: CV = Coefficient of variation</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text in the centre.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The text at the right.</t>
         </r>
       </text>
     </comment>
@@ -97,13 +816,13 @@
     <t xml:space="preserve">title_align</t>
   </si>
   <si>
-    <t xml:space="preserve">table_font_size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title_font_size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">footnote_font_size</t>
+    <t xml:space="preserve">table_font_size_half_points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title_font_size_half_points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footnote_font_size_half_points</t>
   </si>
   <si>
     <t xml:space="preserve">page_header</t>
@@ -815,6 +1534,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -914,6 +1634,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1229,6 +1950,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1346,6 +2068,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1374,6 +2097,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1441,6 +2165,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
